--- a/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
+++ b/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">

--- a/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
+++ b/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -532,44 +532,86 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>富士フイルム製画像読み取り装置及び回診用X 線撮影の保守契約の更新</t>
+          <t>X線透視撮影装置導入に伴う追加備品等一式</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>横浜市立みなと赤十字病院事務部調度課横浜市中区新山下3-12-1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>令和5年9月12日</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>株式会社島津製作所横浜支店横浜市西区北幸2-8-29</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>6290900</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yokohama.jrc.or.jp/wp/wp-content/uploads/2024/10/令和5年度_随意契約の公表.pdf</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>透視撮影台（X線テレビ）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>製品</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>富士フイルム製画像読み取り装置及び回診用X 線撮影の保守契約の更新</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
           <t>横浜市中区新山下3-12-1横浜市立みなと赤十字病院調度課</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>令和7年8月30日</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>富士フイルムメディカル株式会社南関東支社神奈川県横浜市西区高島1-2-13</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>10561452</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>https://www.yokohama.jrc.or.jp/wp/wp-content/uploads/2025/10/随意契約の公表（令和7年度）.pdf</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>一般撮影（レントゲン）</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>保守</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -632,13 +674,9 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">

--- a/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
+++ b/output/横浜市立みなと赤十字病院_随意契約_X線関連.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>一般撮影（レントゲン）</t>
+          <t>回診用X線装置</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -670,33 +670,33 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>透視撮影台（X線テレビ）</t>
+          <t>一般撮影（レントゲン）</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>公表された随意契約に該当なし</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>血管撮影（CVS、アンギオ）</t>
+          <t>透視撮影台（X線テレビ）</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>公表された随意契約に該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
+          <t>血管撮影（CVS、アンギオ）</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -711,7 +711,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>回診用X線装置</t>
+          <t>外科用イメージ（可搬型Cアーム透視装置）</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
